--- a/benchmark/EVM_Manual_Benchmark.xlsx
+++ b/benchmark/EVM_Manual_Benchmark.xlsx
@@ -560,7 +560,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data date    end of Period 6 (Sep-2025)</t>
+          <t>Data date    end of Period 6 (Sep-2026)</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Earned Value by Work Package — end of Period 5 (Aug-2025)</t>
+          <t>Earned Value by Work Package — end of Period 5 (Aug-2026)</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Earned Value by Work Package — end of Period 6 (Sep-2025)</t>
+          <t>Earned Value by Work Package — end of Period 6 (Sep-2026)</t>
         </is>
       </c>
     </row>
